--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_03_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_03_19_Cau.xlsx
@@ -1132,7 +1132,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Reviewer phải biết record nào, từ đâu, vì sao và làm tiếp gì.</t>
+          <t>Một bản ghi trong vùng cách ly (quarantine entry) cần lưu giữ đầy đủ để có thể khắc phục hoặc phục vụ kiểm toán: (a) Dòng dữ liệu gốc hoặc tham chiếu bất biến tới dữ liệu gốc; (b) Quy tắc/lý do vi phạm và bằng chứng lỗi cụ thể; (c) Định danh nguồn và mã định danh lần chạy (Run ID); (d) Người chịu trách nhiệm xem xét, trạng thái xử lý và quyết định replay.</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -1229,7 +1233,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng số phân vùng dự kiến làm mẫu số.</t>
+          <t>Độ bao phủ phân vùng (partition coverage) được tính bằng tỷ lệ phần trăm giữa số phân vùng thực tế xuất hiện trên tổng số phân vùng dự kiến: 228 / 240 = 19 / 20 = 0,95 = 95%.</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1280,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ chấm rule được cung cấp.</t>
+          <t>Đối chiếu bản ghi `{age: 150, email: 'a@b', status: 'active'}` với schema đã cho: (a) Trường age=150 nằm ngoài khoảng cho phép 0..120 nên không hợp lệ; (b) Trường email='a@b' có chứa ký tự '@' nên hợp lệ theo đúng quy tắc kiểm tra đã nêu; (c) Trường status='active' thuộc tập hợp giá trị hợp lệ {active, inactive} nên hợp lệ.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_03_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_03_19_Cau.xlsx
@@ -673,10 +673,21 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chấm từng field theo contract trước khi chấm cả row.
-Phân tích theo nguyên lý thiết kế: Chấm từng field theo contract trước khi chấm cả row.</t>
+- [1.5 điểm] Phân loại đúng disposition cho cả 3 trường: ticket_id bị REJECT do thiếu required key; closed_at được CHẤP NHẬN NULL do status=open; created_at được DERIVE từ signed event timestamp.
+- [1.5 điểm] Đưa ra kết luận tổng thể cho cả bản ghi: do thiếu ticket_id nên bản ghi bị loại (quarantine/DLQ) dù 2 trường kia có thể giải quyết.
+- [1.0 điểm] Thiết lập đầy đủ thông tin data lineage và audit record phục vụ truy vết.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Disposition riêng cho từng field của bản ghi (row status=open, thiếu cả ba trường):
+   - `ticket_id`: DISPOSITION = REJECT / HARD ERROR. Theo contract, `ticket_id` là khóa bắt buộc (required primary key). Bản ghi không có định danh thì không thể tham chiếu, không thể cập nhật và không có giá trị nghiệp vụ -&gt; Phải loại bỏ toàn bộ bản ghi khỏi canonical pipeline và chuyển vào Dead Letter Queue.
+   - `closed_at`: DISPOSITION = ACCEPT AS NULL (Hợp lệ). Theo contract, khi `status=open`, ticket chưa đóng nên `closed_at` là trường tùy chọn và mang giá trị `NULL` là đúng logic nghiệp vụ.
+   - `created_at`: DISPOSITION = RECOVER / DERIVE. Theo contract, `created_at` có thể suy diễn (derive) từ timestamp của signed event trong message metadata. Pipeline tiến hành trích xuất event timestamp từ header, format về ISO-8601 và gán vào `created_at`.
+2. Lineage cần lưu giữ:
+   - Lưu bản ghi thô gốc vào Quarantine/Audit table với cờ lỗi `REJECTED_MISSING_PRIMARY_KEY`;
+   - Ghi nhận metadata lineage: `source_event_id`, `raw_payload_hash`, `validation_rule_failed='ticket_id IS NOT NULL'`, và ghi chú đã phục hồi thử `created_at` từ event timestamp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chính sách xử lý trường thiếu (Field Missingness Policy) phải được đánh giá chi tiết theo từng thuộc tính của hợp đồng dữ liệu (data contract): (1) Khóa chính bắt buộc bị thiếu làm mất tính toàn vẹn thực thể (entity integrity), bắt buộc phải reject; (2) Trường phụ thuộc trạng thái (như closed_at khi status=open) phản ánh đúng ngữ nghĩa nghiệp vụ; (3) Trường có thể suy diễn có nguồn gốc tin cậy (như signed event timestamp) cần được tự động bù đắp kèm theo audit trail.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Great Expectations Core Concepts - Expectation Suites &amp; Missingness Evaluation: https://docs.greatexpectations.io/ và W3C Data Quality Vocabulary: https://www.w3.org/TR/vocab-dqv/</t>
         </is>
       </c>
     </row>
@@ -707,10 +718,20 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách format parsing khỏi việc chứng minh locale của row.
-Phân tích theo nguyên lý thiết kế: Tách format parsing khỏi việc chứng minh locale của row.</t>
+- [1.5 điểm] Chuẩn hóa chính xác 2 bản ghi hợp lệ sang ISO-8601 `2026-04-05` (Input 1 chuẩn ISO, Input 2 theo locale vi là DD/MM/YYYY).
+- [1.5 điểm] Nhận diện chính xác tính mơ hồ (ambiguity giữa 04/05 và 05/04) của bản ghi cuối do thiếu locale provenance.
+- [1.0 điểm] Xử lý an toàn bản ghi cuối: đưa vào quarantine/DLQ, từ chối đoán mò và yêu cầu bổ sung provenance.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Canonicalize các input được hỗ trợ:
+   - Input 1: `2026-04-05` -&gt; Đã đúng định dạng chuẩn ISO-8601 `YYYY-MM-DD`. Kết quả: `2026-04-05` (Ngày 5 tháng 4 năm 2026).
+   - Input 2: `05/04/2026` có locale metadata là `vi` (Việt Nam theo quy ước `DD/MM/YYYY`) -&gt; Parse thành công ngày = 05, tháng = 04, năm = 2026. Kết quả emit chuẩn ISO: `2026-04-05`.
+2. Xử lý bản ghi cuối (`04/05/2026` thiếu locale provenance):
+   - Phân tích rủi ro: Chuỗi `04/05/2026` có thể là ngày 4 tháng 5 năm 2026 (nếu locale `vi`/`en-GB` theo DD/MM) hoặc ngày 5 tháng 4 năm 2026 (nếu locale `en-US` theo MM/DD). Do thiếu hoàn toàn thông tin xuất xứ locale (locale provenance), pipeline không được tự ý phỏng đoán (silent guess).
+   - Xử lý: Đánh dấu bản ghi là `AMBIGUOUS_DATE_FORMAT`, chuyển vào Quarantine Queue / Dead Letter Queue, không đưa vào canonical serving table. Gửi cảnh báo yêu cầu nguồn dữ liệu bổ sung trường header `locale` hoặc chuẩn hóa về ISO trước khi gửi lại.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sự mơ hồ về định dạng ngày tháng (Date Ambiguity Anomaly) giữa quy ước MM/DD/YYYY và DD/MM/YYYY là một trong những nguyên nhân hàng đầu gây sai lệch dữ liệu thời gian. Nguyên tắc thiết kế pipeline nghiêm ngặt quy định: 'Tuyệt đối không đoán mò khi thiếu ngữ cảnh xuất xứ' (No guessing without provenance). Chỉ các chuỗi có định dạng chuẩn ISO hoặc có metadata locale rõ ràng mới được phép canonicalize; các trường hợp mơ hồ phải được cách ly để bảo toàn tính trung thực của dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+ISO 8601 Date and Time Format Standard: https://www.iso.org/iso-8601-date-and-time-format.html và Python `dateutil` Parser Best Practices</t>
         </is>
       </c>
     </row>
@@ -835,10 +856,21 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng sửa từ chuỗi hỏng nếu raw/visual còn là authority.
-Phân tích theo nguyên lý thiết kế: Đừng sửa từ chuỗi hỏng nếu raw/visual còn là authority.</t>
+- [1.5 điểm] Xác định đúng giải pháp recovery: khôi phục trực tiếp từ raw bytes gốc/visual source, không sửa từ chuỗi mojibake đã hỏng.
+- [1.5 điểm] Chỉ ra nguyên nhân gốc ở pipeline trung gian (giải mã sai encoding) và giải pháp sửa chữa triệt để.
+- [1.0 điểm] Thiết kế lineage audit trail ghi nhận quá trình khôi phục và bổ sung quality gate kiểm tra Unicode.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế phương án Recovery (Khôi phục dữ liệu):
+   - Nguyên tắc: Tuyệt đối KHÔNG cố gắng viết hàm sửa ngược từ chuỗi đã bị hỏng mojibake `Nguyá»…n` (vì các phép biến đổi chuỗi hỏng thường mất mát ký tự và thiếu tính đơn định).
+   - Giải pháp: Tận dụng Raw Bytes hoặc Visual Source còn nguyên vẹn làm Source of Truth có thẩm quyền cao nhất. Pipeline quay trở lại bản ghi Raw ban đầu, decode lại trực tiếp từ mảng bytes gốc bằng chuẩn `UTF-8` (hoặc trích xuất lại từ visual source OCR) để tái tạo chính xác tên `Nguyễn`.
+   - Vá lỗi pipeline: Tìm và sửa pipeline trung gian đã gây ra lỗi encoding (thường do đọc byte UTF-8 bằng encoding `windows-1252` hoặc `ISO-8859-1` rồi lại encode UTF-8).
+2. Thiết kế Lineage và Audit Trail:
+   - Ghi lại bản ghi audit: `field='full_name'`, `corrupted_value='Nguyá»…n'`, `restored_value='Nguyễn'`, `recovery_source='raw_bytes_blob'`, `recovery_method='utf8_redecode'`, `timestamp=NOW()`.
+   - Bổ sung Data Quality Gate: Kiểm tra tính hợp lệ của chuỗi Unicode (không chứa các mẫu mojibake phổ biến như `Ã`, `Â`, `»`, `…`) ngay tại đầu ra của mọi stage trung gian.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mojibake xảy ra khi chuỗi byte được mã hóa bằng chuẩn này nhưng lại bị giải mã bằng chuẩn khác trong một trạm trung gian của pipeline. Khi nguồn raw bytes hoặc tài liệu gốc vẫn còn nguyên vẹn, giải pháp an toàn và đáng tin cậy duy nhất là 'Khôi phục từ nguồn có thẩm quyền' (Recover from Authoritative Source), thay vì cố gắng đảo ngược chuỗi hỏng bằng heuristic. Đồng thời, phải thiết lập rào chắn kiểm thử encoding tại mọi bước chuyển dữ liệu để ngăn tái diễn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Unicode Standard Annex #44 - Unicode Character Database: https://www.unicode.org/reports/tr44/ và Python Unicode HOWTO: https://docs.python.org/3/howto/unicode.html</t>
         </is>
       </c>
     </row>
@@ -869,10 +901,22 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Cùng order chưa chắc là cùng event/version.
-Phân tích theo nguyên lý thiết kế: Cùng order chưa chắc là cùng event/version.</t>
+- [1.5 điểm] Định nghĩa đúng business key là composite `(order_id, version)` và phân biệt rõ ràng giữa versioning (A vs B) và true duplicate (B vs D).
+- [1.5 điểm] Lựa chọn bản ghi survivor chính xác theo ngữ cảnh (giữ version 2 cao nhất cho current state và khử trùng lặp giữa B và D).
+- [1.0 điểm] Thiết lập audit trail chi tiết cho bản ghi bị loại bỏ (deduplication audit log).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Định nghĩa Business Key và Phân biệt Version vs Duplicate:
+   - Phân tích: Đơn hàng số 7 có các bản ghi với `version=1` và `version=2`. Cùng `order=7` không đồng nghĩa là trùng lặp, mà đây là các trạng thái thay đổi theo thời gian (State Progression / Event Versioning).
+   - Business Key thực sự: Cặp composite key `(order_id, version)`.
+   - Phân loại: Dòng A (7, 1, pending) là phiên bản 1; Dòng B (7, 2, paid) và Dòng D (7, 2, paid) cùng có khóa `(order=7, version=2)` và cùng nguồn/hash -&gt; D và B là bản sao trùng lặp thực sự (True Duplicate). Dòng C (8, 1, paid) là đơn hàng khác hoàn toàn.
+2. Chọn Survivor (Bản ghi sống sót) và Audit:
+   - Nếu mô hình hóa Snapshot hiện hành (Current State): Chọn bản ghi có `order_id` duy nhất với `version` cao nhất -&gt; Với order 7, chọn phiên bản 2 (`version=2, status=paid`); giữa B và D chỉ giữ lại 1 dòng duy nhất (Deduplication).
+   - Nếu mô hình hóa Lịch sử sự kiện (Event Log / SCD Type 2): Giữ cả A (version 1) và một bản thể duy nhất của B (version 2).
+   - Audit Trail: Ghi log dòng D bị khử trùng lặp (deduplicated) kèm `duplicate_of=B_row_id`, `dedup_rule='exact_hash_match'`, `timestamp=NOW()`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Việc khử trùng lặp dữ liệu (Deduplication) đòi hỏi phải phân biệt sâu sắc giữa 'Trùng lặp kỹ thuật' (Technical Duplicate - hai bản ghi giống hệt nhau gửi lặp) và 'Tiến trình nghiệp vụ' (Business Versioning - cùng entity nhưng khác version/trạng thái). Khóa kinh doanh phải phản ánh đúng chiều thời gian hoặc phiên bản sự kiện. Việc chọn survivor phụ thuộc vào mục tiêu lưu trữ (tổng hợp trạng thái cuối hay lưu vết toàn bộ lịch sử biến đổi).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Ralph Kimball, The Data Warehouse Toolkit - Slowly Changing Dimensions (SCD Type 2) và Martin Kleppmann, Designing Data-Intensive Applications - Idempotency &amp; Deduplication</t>
         </is>
       </c>
     </row>
@@ -948,10 +992,24 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi native field cần một declared mapping, không phải đoán tên.
-Phân tích theo nguyên lý thiết kế: Mỗi native field cần một declared mapping, không phải đoán tên.</t>
+- [1.5 điểm] Thực hiện chính xác toàn bộ 3 phép mapping: ticket_id thành chuỗi '42', urgency 'high' thành 'P1', date thành ISO '2026-04-05'.
+- [1.5 điểm] Đối chiếu và kiểm định đầy đủ từng trường với các điều kiện ràng buộc của canonical schema.
+- [1.0 điểm] Đưa ra kết luận rõ ràng (VALID, PASS) và cấu trúc bản ghi canonical hoàn chỉnh.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thực hiện Mapping dữ liệu theo declared contract:
+   - `ticket_id: 42` -&gt; ép kiểu chuỗi thành `id: '42'` (thỏa mãn `id:str required`).
+   - `urgency: 'high'` -&gt; ánh xạ theo rule `high -&gt; P1` thành `priority: 'P1'` (thỏa mãn `priority ∈ {P1, P2, P3}`).
+   - `date: '05/04/2026'` với metadata `locale=vi` (ngày/tháng/năm) -&gt; parse thành ngày 05 tháng 04 năm 2026, chuyển sang ISO date: `created_at: '2026-04-05'`.
+2. Validate đối chiếu với Canonical Schema:
+   - Kết quả bản ghi sau mapping: `{'id': '42', 'priority': 'P1', 'created_at': '2026-04-05'}`.
+   - Kiểm tra: `id` có kiểu chuỗi và không rỗng (PASS); `priority` thuộc tập hợp cho phép `{P1, P2, P3}` (PASS); `created_at` đúng chuẩn ISO-8601 date (PASS).
+3. Báo cáo kết quả:
+   - Trạng thái: VALID (Thành công 100%).
+   - Output Artifact: Dòng canonical hoàn chỉnh được bàn giao cho tầng tiếp theo (enrichment/indexing), kèm theo audit log mapping.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mapping từ cấu trúc bản xứ (native schema) sang cấu trúc chuẩn mực (canonical schema) phải được định nghĩa bằng các hợp đồng biến đổi tường minh (explicit declared mappings), không được dựa trên việc suy đoán ngẫu nhiên. Sau khi mapping hoàn tất, bản ghi bắt buộc phải vượt qua bộ kiểm thử schema xác thực kiểu dữ liệu, các ràng buộc giá trị (enum set) và định dạng ngày chuẩn trước khi được đưa vào kho dữ liệu chính thức.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pydantic V2 Documentation - Data Validation and Settings Management: https://docs.pydantic.dev/ và Great Expectations - Expect Column Values To Be In Set: https://docs.greatexpectations.io/</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1136,21 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách “sửa chắc chắn được”, “không recover”, “cần người xem” và “soft issue”.
-Phân tích theo nguyên lý thiết kế: Tách “sửa chắc chắn được”, “không recover”, “cần người xem” và “soft issue”.</t>
+- [1.5 điểm] Chọn đúng disposition cho cả 4 trường hợp: A auto-repair, B reject/DLQ, C quarantine/human review, D accept with warning.
+- [1.5 điểm] Phân tích lý do kỹ thuật thuyết phục cho từng lựa chọn dựa trên mức độ nghiêm trọng và khả năng phục hồi.
+- [1.0 điểm] Trình bày rõ hệ quả đối với các tầng xử lý downstream (chỉ bản ghi sạch mới được index vào phục vụ agent).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn Disposition cho từng bản ghi A-D:
+   - Bản ghi A (chỉ thừa khoảng trắng whitespace): DISPOSITION = AUTO-REPAIR / ACCEPT. Hành động: Tự động chạy hàm `strip()` loại bỏ whitespace đầu/cuối và chuẩn hóa khoảng cách giữa các từ, chuyển vào canonical dataset bình thường.
+   - Bản ghi B (mất required account_id không có nguồn khôi phục): DISPOSITION = REJECT / DROP TO DLQ. Hành động: Loại bỏ khỏi luồng chính, lưu vào Dead Letter Queue vĩnh viễn kèm log lỗi vi phạm khóa bắt buộc.
+   - Bản ghi C (OCR amount bị mờ nhưng visual gốc còn nguyên): DISPOSITION = QUARANTINE / HUMAN REVIEW. Hành động: Đưa vào hàng đợi duyệt thủ công (HITL), đính kèm file ảnh visual gốc để nhân viên kế toán đối chiếu và nhập lại số tiền chính xác.
+   - Bản ghi D (optional comment dài hơn soft limit): DISPOSITION = ACCEPT WITH WARNING / TRUNCATE WITH NOTE. Hành động: Cắt ngắn (truncate) theo độ dài cho phép hoặc lưu nguyên vẹn tùy cấu hình, ghi nhận một cảnh báo (warning log) nhưng vẫn cho phép đi tiếp vào pipeline.
+2. Nêu hệ quả ở tầng sau:
+   - Tầng Vector Index / RAG Agent: A và D được index an toàn; B không xuất hiện trong hệ thống; C bị hoãn cho đến khi con người phê duyệt xong mới được index bổ sung.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chính sách phân loại bản ghi (Record Disposition Policy) cần phân biệt rạch ròi 4 cấp độ hỏng hóc: (1) Sửa chắc chắn được bằng thuật toán đơn định (whitespace -&gt; auto-clean); (2) Lỗi nghiêm trọng không thể khắc phục (missing primary key -&gt; reject/DLQ); (3) Mất mát thông tin nhưng nguồn gốc còn để phục hồi (OCR mờ -&gt; quarantine review); (4) Lỗi nhẹ không ảnh hưởng toàn vẹn nghiệp vụ (soft limit -&gt; warning pass). Phân loại chính xác giúp tối đa hóa throughput mà không làm giảm chất lượng dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+DAMA-DMBOK: Data Quality Management &amp; Exception Handling Rules; Google Cloud Architecture Framework - Data Processing Error Handling</t>
         </is>
       </c>
     </row>
@@ -1163,10 +1232,27 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Replay cần chứng minh điều gì đã thay đổi kể từ lúc fail?
-Phân tích theo nguyên lý thiết kế: Replay cần chứng minh điều gì đã thay đổi kể từ lúc fail?</t>
+- [1.5 điểm] Xây dựng schema quarantine đầy đủ các trường thiết yếu: run_id, raw_payload, source_system, failure_code/reason, quarantined_at, status.
+- [1.5 điểm] Thiết kế cơ chế Replay Guard với điều kiện tiên quyết chứng minh sự thay đổi (code update hoặc data fix).
+- [1.0 điểm] Đưa ra cơ chế chống lặp (idempotency key / hash) khi replay để ngăn chặn vòng lặp lỗi tái diễn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Schema Quarantine chuẩn mực:
+   - `quarantine_id`: UUID duy nhất cho sự kiện cách ly.
+   - `run_id`: Định danh của pipeline run đã phát hiện lỗi.
+   - `source_system` &amp; `source_file_id`: Nguồn gốc sinh ra dữ liệu.
+   - `raw_payload`: Toàn bộ dữ liệu thô ban đầu (JSON string / raw bytes) để phục vụ tái hiện.
+   - `parsed_canonical_partial`: Dữ liệu đã parse một phần trước khi vấp lỗi.
+   - `failure_code` &amp; `failure_reason`: Mã lỗi (`MISSING_REQUIRED_FIELD`, `INVALID_REGEX`) và thông điệp chi tiết.
+   - `failed_field`: Tên trường dữ liệu gây ra vi phạm.
+   - `quarantined_at`: Timestamp thời điểm bản ghi bị chuyển cách ly.
+   - `status`: Trạng thái xử lý (`PENDING`, `REPLAYED`, `DISCARDED`).
+2. Thiết kế Replay Guard (Rào chắn an toàn khi chạy lại):
+   - Điều kiện kiểm chứng tiên quyết: Trước khi replay một bản ghi từ quarantine, hệ thống phải chứng minh 'Điều gì đã thay đổi kể từ lúc lỗi xảy ra' (ví dụ: phiên bản code pipeline đã tăng từ v1.2 lên v1.3 để sửa bug parser, hoặc bản ghi đã được con người cập nhật lại trường thiếu).
+   - Khóa chống trùng lặp (Idempotency Key): Sử dụng `hash(raw_payload + new_code_version)` để đảm bảo nếu chạy lại mà code chưa sửa hoặc dữ liệu chưa đổi thì sẽ bị từ chối replay ngay lập tức.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một file `dropped_rows.csv` chỉ chứa dữ liệu canonical là một thiết kế 'mù' (blind drop), bởi vì nó đã làm mất thông tin raw gốc, không biết lỗi gì và phát sinh từ run nào, khiến việc debug và replay trở nên bất khả thi. Schema cách ly (Quarantine Schema) phải lưu giữ đầy đủ ngữ cảnh thất bại và bằng chứng nguyên bản. Rào chắn Replay Guard ngăn chặn việc người vận hành chạy lại một cách mù quáng (blind retry) khi các điều kiện gây lỗi chưa hề được khắc phục.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Enterprise Integration Patterns - Dead Letter Channel: https://www.enterpriseintegrationpatterns.com/patterns/messaging/DeadLetterChannel.html và Martin Fowler, 'Accounting Patterns' - Audit Log &amp; Reversibility</t>
         </is>
       </c>
     </row>
@@ -1197,10 +1283,25 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính hai tỷ lệ với hai mẫu số khác nhau.
-Phân tích theo nguyên lý thiết kế: Tính hai tỷ lệ với hai mẫu số khác nhau.</t>
+- [1.5 điểm] Tính toán chính xác 2 tỷ lệ riêng biệt: Độ bao phủ bản ghi = 90/100 (90%) và Độ đầy đủ email trên bản ghi nhận được = 81/90 (90%).
+- [1.5 điểm] Nêu rõ sự khác biệt giữa hai mẫu số (mẫu số 100 của hợp đồng vs mẫu số 90 của batch nhận).
+- [1.0 điểm] Chỉ ra chính xác các điều chưa được chứng minh: tính hợp lệ cú pháp email, tính chính xác thực thể và nguyên nhân thất thoát 10 bản ghi.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán các chỉ số chất lượng dữ liệu:
+   - Độ bao phủ bản ghi (Record Coverage Rate / Completeness of Rows):
+     Tỷ lệ = (Số bản ghi thực tế nhận được) / (Số bản ghi hợp đồng kỳ vọng)
+     Tỷ lệ = 90 / 100 = 0.90 (90.0%).
+   - Độ đầy đủ trường email (Email Field Completeness Rate on Received Records):
+     Tỷ lệ = (Số bản ghi có email hợp lệ trong các bản ghi đã nhận) / (Tổng số bản ghi đã nhận)
+     Tỷ lệ = 81 / 90 = 0.90 (90.0%).
+   - Độ đầy đủ trường email toàn diện (Overall Email Completeness against Contract):
+     Tỷ lệ = 81 / 100 = 0.81 (81.0%).
+2. Nêu điều chưa được chứng minh (Unproven Aspect):
+   - Việc trường email có mặt (81 bản ghi) mới chỉ chứng minh 'tính không rỗng' (non-nullness), CHƯA chứng minh được: (a) Tính hợp lệ định dạng cú pháp (valid email regex format - e.g. có chứa ký tự rác hay không); (b) Tính chính xác thực tế (email có tồn tại và thuộc về đúng user đó hay không); (c) Nguyên nhân mất 10 bản ghi đầu nguồn (10 missing records) là do source chưa gửi hay do bị rớt mạng trong quá trình truyền dẫn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiểm định độ đầy đủ dữ liệu (Completeness Measurement), một sai lầm phổ biến là nhầm lẫn giữa hai mẫu số: (1) Mẫu số theo hợp đồng kỳ vọng (đo lường độ rò rỉ luồng dữ liệu - stream drop) và (2) Mẫu số theo dữ liệu thực nhận (đo lường chất lượng trường trong nội bộ batch). Phải tách biệt rõ ràng độ bao phủ bản ghi (Row Coverage) và độ đầy đủ thuộc tính (Field Completeness). Đồng thời, dữ liệu có mặt không đồng nghĩa với dữ liệu chính xác (presence != correctness).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+ISO/IEC 25012: Data Quality Model - Completeness and Accuracy Dimensions; Great Expectations - Expect Column Values To Not Be Null</t>
         </is>
       </c>
     </row>
@@ -1311,10 +1412,25 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chuỗi có hình dạng ngày chưa chắc biểu diễn một ngày tồn tại.
-Phân tích theo nguyên lý thiết kế: Chuỗi có hình dạng ngày chưa chắc biểu diễn một ngày tồn tại.</t>
+- [1.5 điểm] Thiết kế expectation chính xác: phân biệt kiểm tra regex hình thức và kiểm tra parser lịch thực thụ (strict calendar date parsing).
+- [1.5 điểm] Xây dựng cấu trúc báo cáo vi phạm (violation report) đầy đủ: tên cột, giá trị vi phạm, loại lỗi và thông điệp giải thích cụ thể.
+- [1.0 điểm] Đưa ra giải pháp xử lý bản ghi vi phạm (chặn hard gate, chuyển quarantine).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Expectation (Quy tắc kiểm thử tính hợp lệ ngữ nghĩa):
+   - Không dừng lại ở việc kiểm tra Regex định dạng: Biểu thức chính quy `^\d{4}-\d{2}-\d{2}$` chỉ xác nhận chuỗi có hình dạng ngày, nhưng hoàn toàn bất lực trước các ngày không có thực trên lịch (như 30/02/2026).
+   - Expectation chuẩn (Semantic Calendar Validation): Sử dụng parser lịch thực thụ (như `datetime.strptime(val, '%Y-%m-%d')` trong Python hoặc `TO_DATE(val, 'YYYY-MM-DD')` với strict mode). Quy tắc này sẽ kích hoạt ngoại lệ `ValueError: day is out of range for month` khi gặp ngày 30 tháng 2 (năm 2026 không nhuận và tháng 2 chỉ có 28 ngày).
+2. Báo cáo vi phạm (Violation Report Schema):
+   - `expectation_name`: `expect_column_values_to_be_valid_calendar_date`
+   - `column`: `event_date`
+   - `invalid_value`: `'2026-02-30'`
+   - `violation_type`: `SEMANTIC_INVALID_DATE`
+   - `error_message`: `Date '2026-02-30' does not exist in Gregorian calendar (February 2026 has only 28 days)`
+   - `severity`: `ERROR / HARD_GATE`
+   - `disposition`: Cách ly bản ghi vào Quarantine Queue để rà soát nguồn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc 'Hình thức hợp lệ không bảo đảm thực tại hợp lệ' (Syntactic Validity != Semantic Validity) là bài học kinh điển trong kỹ nghệ dữ liệu. Một chuỗi ký tự khớp hoàn hảo với cấu trúc regex `YYYY-MM-DD` vẫn có thể biểu diễn một giá trị vô lý trong thế giới thực. Do đó, các bộ kiểm định dữ liệu (Data Quality Suites) bắt buộc phải sử dụng các thư viện kiểm tra ngữ nghĩa chuyên dụng (calendar parsers) và sinh ra báo cáo vi phạm chi tiết phục vụ debug.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Great Expectations - Expect Column Values To Be Dateutil Parseable: https://greatexpectations.io/ và Python `datetime` Standard Library Documentation</t>
         </is>
       </c>
     </row>
@@ -1345,10 +1461,24 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một đơn hàng có thể có nhiều dòng hàng hợp lệ.
-Phân tích theo nguyên lý thiết kế: Một đơn hàng có thể có nhiều dòng hàng hợp lệ.</t>
+- [1.5 điểm] Lựa chọn chính xác composite key là (order_id, line_id) theo đúng hợp đồng nghiệp vụ.
+- [1.5 điểm] Tính toán chính xác số liệu: có đúng 1 nhóm trùng lặp (1, A) và đúng 1 dòng dư thừa cần loại bỏ.
+- [1.0 điểm] Phân biệt rõ ràng tính hợp lệ của dòng (2, A) so với (1, A) dựa trên phạm vi đơn hàng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn Khóa Duy Nhất (Uniqueness Key):
+   - Theo hợp đồng: 'mỗi dòng hàng là duy nhất trong một đơn hàng'. Do đó, khóa duy nhất bắt buộc phải là cặp Composite Key: `(order_id, line_id)`.
+2. Phân tích các dòng dữ liệu và Tính toán:
+   - Tập dữ liệu gồm 4 dòng: D1(1, A), D2(1, B), D3(1, A), D4(2, A).
+   - Nhóm theo Composite Key `(order_id, line_id)`:
+     + Nhóm `(1, A)`: xuất hiện 2 lần (D1 và D3) -&gt; TRÙNG LẶP.
+     + Nhóm `(1, B)`: xuất hiện 1 lần (D2) -&gt; Duy nhất.
+     + Nhóm `(2, A)`: xuất hiện 1 lần (D4) -&gt; Duy nhất (dù cùng line_id='A' nhưng thuộc order_id khác, hoàn toàn hợp lệ theo contract).
+   - Số nhóm trùng lặp (Duplicate Groups Count): Có đúng 1 nhóm trùng lặp, đó là nhóm khóa `(1, A)`.
+   - Số dòng dư thừa (Redundant / Duplicate Rows Count): Trong nhóm `(1, A)` có 2 dòng, chỉ giữ lại 1 dòng survivor, do đó có 1 dòng dư thừa cần bị loại bỏ (2 - 1 = 1 dòng dư).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong các mô hình dữ liệu quan hệ và bán cấu trúc, một thuộc tính định danh cấp con (như line_id) thường chỉ có ý nghĩa trong phạm vi của một thực thể cha (như order_id). Việc chỉ chọn line_id làm khóa sẽ dẫn đến kết luận sai lầm rằng (1, A) và (2, A) bị trùng. Việc thiết lập đúng Composite Key `(order_id, line_id)` cho phép phân định chính xác số nhóm trùng lặp (1 nhóm) và số bản ghi rác cần khử (1 bản ghi dư thừa), bảo toàn tính toàn vẹn của đơn hàng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+SQL Standards for Primary Key &amp; Composite Constraints; Great Expectations - Expect Compound Columns To Be Unique: https://docs.greatexpectations.io/</t>
         </is>
       </c>
     </row>
